--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Testing and Secure Coding/GroupAssignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="11_54D282350BB20B8CABA1FC287F7825C14AB2CAC7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6A1DB2-1469-4E5E-800B-7AE759333CC9}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="11_54D282350BB20B8CABA1FC287F7825C14AB2CAC7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F6AD3A-E60F-47D7-A035-EDEBE3770485}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="82">
   <si>
     <t>Project Name:</t>
   </si>
@@ -125,9 +125,6 @@
     <t>Richa Panjabi</t>
   </si>
   <si>
-    <t>The Full Metal Library website will be where a librarian can add new items, register new users, and have the users checkout the items.</t>
-  </si>
-  <si>
     <t>As a new administrator, I want to register to the application, so that I can use it.</t>
   </si>
   <si>
@@ -276,13 +273,25 @@
   </si>
   <si>
     <t>Reasoning behind priority setting method: The CRUD implementation for the Book, Author, and Admin classes would be easy to implement, so we decided to put them in the first sprint. The Search/Sort functionality would be a little harder, and also requires the pages to be set up first, so that went in sprint 2.</t>
+  </si>
+  <si>
+    <t>Users should be able to log into the site.</t>
+  </si>
+  <si>
+    <t>Users should be able to manage Books.</t>
+  </si>
+  <si>
+    <t>Users should be able to manage Authors</t>
+  </si>
+  <si>
+    <t>Users should be able to manage accounts to sign in with</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,10 +325,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -344,7 +349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -382,26 +387,176 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -409,38 +564,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -458,6 +696,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -662,11 +904,11 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
-    <col min="2" max="2" width="44.85546875" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" customWidth="1"/>
     <col min="9" max="9" width="33.140625" customWidth="1"/>
@@ -674,604 +916,617 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
+      <c r="F8" s="11">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:26" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18">
+        <v>2</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+    </row>
+    <row r="14" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="18">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18">
+        <v>2</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+    </row>
+    <row r="16" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="25">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25">
+        <v>1</v>
+      </c>
+      <c r="G16" s="26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1">
+    <row r="17" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="23">
+        <v>1</v>
+      </c>
+      <c r="F17" s="23">
+        <v>1</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="23">
+        <v>1</v>
+      </c>
+      <c r="F18" s="23">
+        <v>1</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="23">
         <v>2</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
+      <c r="F19" s="23">
+        <v>2</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="9" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="1">
+    <row r="20" spans="1:7" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="30">
+        <v>1</v>
+      </c>
+      <c r="F20" s="30">
         <v>2</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G20" s="31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="34">
+        <v>1</v>
+      </c>
+      <c r="F21" s="34">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36"/>
+      <c r="B22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="32">
+        <v>1</v>
+      </c>
+      <c r="F22" s="32">
+        <v>1</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36"/>
+      <c r="B23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="32">
+        <v>1</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36"/>
+      <c r="B24" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="32">
+        <v>1</v>
+      </c>
+      <c r="F24" s="32">
         <v>2</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
+      <c r="G24" s="37" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="1">
+    <row r="25" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36"/>
+      <c r="B25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="32">
+        <v>2</v>
+      </c>
+      <c r="F25" s="32">
+        <v>2</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
+      <c r="B26" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="39">
         <v>1</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F26" s="39">
         <v>2</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-    </row>
-    <row r="11" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-    </row>
-    <row r="12" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-    </row>
-    <row r="13" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-    </row>
-    <row r="14" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-    </row>
-    <row r="15" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-    </row>
-    <row r="16" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+      <c r="G26" s="40" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9">
-        <v>1</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9">
-        <v>2</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="9">
-        <v>2</v>
-      </c>
-      <c r="F25" s="9">
-        <v>2</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9">
-        <v>2</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:7" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="13" t="s">
-        <v>78</v>
+    <row r="28" spans="1:7" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2247,8 +2502,11 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A8:A19"/>
+  <mergeCells count="4">
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
